--- a/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
+++ b/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R689b316e174e4172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R72c8c685fc7a4049"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -801,15 +801,19 @@
         </x:is>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
-        <x:v>Refund/reconcile APIs exist; operator UI screens remain open.</x:v>
-      </x:c>
-      <x:c r="I10" s="3" t="str"/>
-      <x:c r="J10" s="3" t="str"/>
+        <x:v>Admin payment details expose refund eligibility, reason/method input, persisted refund/audit history, manual gateway completion, wallet refunds, and reconciliation. FinanceManage protects money-moving actions; server locks and idempotency prevent duplicates.</x:v>
+      </x:c>
+      <x:c r="I10" s="3" t="str">
+        <x:v>AdminPaymentsController; PaymentsController; PaymentService; AdminPaymentReadService; Admin Payments UI; finance integration tests</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
+        <x:v>bc43474, 928bb81</x:v>
+      </x:c>
       <x:c r="K10" s="3" t="str">
-        <x:v>Existing finance integration tests only</x:v>
+        <x:v>Release build; unit 409/409; integration 114/114; Admin Playwright 7/7</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">

--- a/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
+++ b/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R72c8c685fc7a4049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R6a6cb7b52f9243d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -942,19 +942,19 @@
         </x:is>
       </x:c>
       <x:c r="G13" s="3" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H13" s="3" t="str">
-        <x:v>One idempotent support ticket per order exists; multi-item assignment/semantics still need product-policy confirmation.</x:v>
+        <x:v>Exactly one automatic fulfilment ticket is created per qualifying order, with every SupportRequired OrderItem linked to it. Customer-created order tickets stay separate. A filtered unique database index, payment idempotency, and safe retry preserve the invariant under replay and concurrency.</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>PaymentService; PaymentDeliveryIntegrationTests</x:v>
+        <x:v>V0007; Ticket/OrderItem model; DbContext; PaymentService; TicketService; ticket DTOs and Admin/Customer ticket UI; support integration and Playwright tests</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>39024e2</x:v>
+        <x:v>ffa9658, 058148f, 24a149f, aed83ff</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
-        <x:v>Existing support integration coverage</x:v>
+        <x:v>Release build 0 warnings; unit 410/410; SQL integration 117/117; focused browser Customer/Admin support flow 1/1 (57.1s); clean migration + upgrade rehearsal verified</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">

--- a/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
+++ b/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R6a6cb7b52f9243d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="Rcf39f464224d43cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -989,15 +989,19 @@
         </x:is>
       </x:c>
       <x:c r="G14" s="3" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H14" s="3" t="str">
-        <x:v>Core filters/pagination exist but catalog refinements are still partly client-side.</x:v>
-      </x:c>
-      <x:c r="I14" s="3" t="str"/>
-      <x:c r="J14" s="3" t="str"/>
+        <x:v>Storefront paging, counts, product type, delivery, verification, price, availability, and discount-tier filters now execute in the public catalog query. Invalid price ranges and discount thresholds are rejected server-side; the UI only owns filter state.</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="str">
+        <x:v>ProductFilterDto; ProductService; ShopBrowser; catalog unit and SQL integration tests</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
+        <x:v>9f885dc</x:v>
+      </x:c>
       <x:c r="K14" s="3" t="str">
-        <x:v>Audit evidence retained</x:v>
+        <x:v>Release build 0 warnings; focused unit 3/3; SQL-backed catalog API integration 1/1; storefront Playwright 1/1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">

--- a/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
+++ b/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="Rcf39f464224d43cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="Raf5224dd7f254b3d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1167,15 +1167,19 @@
         </x:is>
       </x:c>
       <x:c r="G18" s="3" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Progress</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
-        <x:v>Several admin screens still load unbounded lists or use client paging.</x:v>
-      </x:c>
-      <x:c r="I18" s="3" t="str"/>
-      <x:c r="J18" s="3" t="str"/>
+        <x:v>Completed inventory in docs/REQ-010-ADMIN-PAGING-INVENTORY.md. Products, orders, payments, wallets, tickets, verification, and audit/error/security operational logs now use SQL-side filtered, counted, stable paged endpoints; legacy endpoints remain compatible. Notifications and coupons now expose the same bounded contract. Remaining: migrate their UI/export semantics, bounded lookup sources, focused paging tests, and full verification.</x:v>
+      </x:c>
+      <x:c r="I18" s="3" t="str">
+        <x:v>Admin paging inventory; Admin Products/Orders/Payments/Wallets/Tickets/Verifications/AuditLogs/ErrorLogs/SecurityLogs; paged controllers and read services</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="str">
+        <x:v>8b5fdf7, a885f5c, 02d3354</x:v>
+      </x:c>
       <x:c r="K18" s="3" t="str">
-        <x:v>Repository inspection</x:v>
+        <x:v>Release builds passed (0 warnings after incremental); focused SQL AdminCatalog suite 3/3</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="44" customHeight="1">

--- a/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
+++ b/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="Raf5224dd7f254b3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R6702fc8ea6514a4a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1170,16 +1170,16 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
-        <x:v>Completed inventory in docs/REQ-010-ADMIN-PAGING-INVENTORY.md. Products, orders, payments, wallets, tickets, verification, and audit/error/security operational logs now use SQL-side filtered, counted, stable paged endpoints; legacy endpoints remain compatible. Notifications and coupons now expose the same bounded contract. Remaining: migrate their UI/export semantics, bounded lookup sources, focused paging tests, and full verification.</x:v>
+        <x:v>Completed inventory in docs/REQ-010-ADMIN-PAGING-INVENTORY.md. Products, orders, payments, wallets, tickets, verification, notifications, coupons, and audit/error/security operational logs now use SQL-side filtered, counted, stable paged endpoints; legacy endpoints remain compatible. Gift-code product selection uses a dedicated bounded lookup. Remaining: detail-history paging, explicit export semantics, focused paging tests, and full verification.</x:v>
       </x:c>
       <x:c r="I18" s="3" t="str">
-        <x:v>Admin paging inventory; Admin Products/Orders/Payments/Wallets/Tickets/Verifications/AuditLogs/ErrorLogs/SecurityLogs; paged controllers and read services</x:v>
+        <x:v>Admin paging inventory; Admin Products/Orders/Payments/Wallets/Tickets/Verifications/Notifications/Coupons/AuditLogs/ErrorLogs/SecurityLogs; paged controllers/read services; GiftCodes lookup</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>8b5fdf7, a885f5c, 02d3354</x:v>
+        <x:v>8b5fdf7, a885f5c, 02d3354, cd98354, eaee518</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
-        <x:v>Release builds passed (0 warnings after incremental); focused SQL AdminCatalog suite 3/3</x:v>
+        <x:v>Release builds passed (0 warnings after incremental); focused SQL AdminCatalog suite 3/3; new SQL test host currently hangs before execution and was not retained</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="44" customHeight="1">

--- a/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
+++ b/outputs/launch-hardening/Vitorize_Launch_Hardening_Backlog.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R6702fc8ea6514a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Launch Hardening" sheetId="1" r:id="R1ace12b092d74bd9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -393,7 +393,7 @@
         <x:v>Test Results</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="44" customHeight="1">
+    <x:row r="2" ht="90" customHeight="1">
       <x:c r="A2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RB-001</x:t>
@@ -440,7 +440,7 @@
         <x:v>Release build; 396 unit; Commerce integration 5/5</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="44" customHeight="1">
+    <x:row r="3" ht="90" customHeight="1">
       <x:c r="A3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RB-002</x:t>
@@ -487,7 +487,7 @@
         <x:v>Release build; 396 unit</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="44" customHeight="1">
+    <x:row r="4" ht="90" customHeight="1">
       <x:c r="A4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RB-003</x:t>
@@ -534,7 +534,7 @@
         <x:v>dotnet list package --vulnerable: clean</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="44" customHeight="1">
+    <x:row r="5" ht="90" customHeight="1">
       <x:c r="A5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RB-004</x:t>
@@ -581,7 +581,7 @@
         <x:v>Deployment asset test passed; Commerce SQL integration previously passed 5/5</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="44" customHeight="1">
+    <x:row r="6" ht="90" customHeight="1">
       <x:c r="A6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RB-005</x:t>
@@ -628,7 +628,7 @@
         <x:v>Release build; 12 focused configuration/fault tests passed</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" ht="90" customHeight="1">
       <x:c r="A7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RB-006</x:t>
@@ -675,7 +675,7 @@
         <x:v>All backup PowerShell scripts parsed successfully</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+    <x:row r="8" ht="90" customHeight="1">
       <x:c r="A8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RB-007</x:t>
@@ -722,7 +722,7 @@
         <x:v>Release build; 400 unit; ApiSecurity SQL integration 17/17</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="44" customHeight="1">
+    <x:row r="9" ht="90" customHeight="1">
       <x:c r="A9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-001</x:t>
@@ -769,7 +769,7 @@
         <x:v>Release build 0 warnings; unit 409/409; integration 113/113; Playwright auth 36/36</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="44" customHeight="1">
+    <x:row r="10" ht="90" customHeight="1">
       <x:c r="A10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-002</x:t>
@@ -816,7 +816,7 @@
         <x:v>Release build; unit 409/409; integration 114/114; Admin Playwright 7/7</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="44" customHeight="1">
+    <x:row r="11" ht="90" customHeight="1">
       <x:c r="A11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-003</x:t>
@@ -863,7 +863,7 @@
         <x:v>Release build; 396 unit</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="44" customHeight="1">
+    <x:row r="12" ht="90" customHeight="1">
       <x:c r="A12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-004</x:t>
@@ -910,7 +910,7 @@
         <x:v>Focused Commerce/SQL integration remains green</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="44" customHeight="1">
+    <x:row r="13" ht="90" customHeight="1">
       <x:c r="A13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-005</x:t>
@@ -957,7 +957,7 @@
         <x:v>Release build 0 warnings; unit 410/410; SQL integration 117/117; focused browser Customer/Admin support flow 1/1 (57.1s); clean migration + upgrade rehearsal verified</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="44" customHeight="1">
+    <x:row r="14" ht="90" customHeight="1">
       <x:c r="A14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-006</x:t>
@@ -1004,7 +1004,7 @@
         <x:v>Release build 0 warnings; focused unit 3/3; SQL-backed catalog API integration 1/1; storefront Playwright 1/1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="44" customHeight="1">
+    <x:row r="15" ht="90" customHeight="1">
       <x:c r="A15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-007</x:t>
@@ -1036,20 +1036,22 @@
         </x:is>
       </x:c>
       <x:c r="G15" s="3" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
-        <x:v>Recent visual-baseline fixes exist; all-project visual regression must be rerun before completion.</x:v>
+        <x:v>Visual tests now exercise a fixed, server-side cheapest category sort instead of mutable recency. Public catalog ordering is total with Id tie-breakers. Dynamic home/admin regions remain intentionally masked or bounded; fresh-reset captures reapproved only after the deterministic state was verified.</x:v>
       </x:c>
       <x:c r="I15" s="3" t="str">
-        <x:v>tests/Vitorize.E2E</x:v>
-      </x:c>
-      <x:c r="J15" s="3" t="str"/>
+        <x:v>ProductService; Store Category; visual-regression.spec.ts; approved visual snapshots; ProductExperienceIntegrationTests</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="str">
+        <x:v>265008e</x:v>
+      </x:c>
       <x:c r="K15" s="3" t="str">
-        <x:v>Not rerun in this milestone</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="44" customHeight="1">
+        <x:v>Release build 0 warnings/0 errors; focused catalog unit 4/4; full unit 422/422; SQL integration 124/124; all-project visual Playwright 6/6 after pristine reset (1.2m), teardown clean.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="90" customHeight="1">
       <x:c r="A16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-008</x:t>
@@ -1081,18 +1083,22 @@
         </x:is>
       </x:c>
       <x:c r="G16" s="3" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Blocked - External Dependency</x:v>
       </x:c>
       <x:c r="H16" s="3" t="str">
-        <x:v>No checked-in CI workflow was found.</x:v>
-      </x:c>
-      <x:c r="I16" s="3" t="str"/>
-      <x:c r="J16" s="3" t="str"/>
+        <x:v>Added a GitHub Actions release gate for pull requests, pushes and manual runs: zero-warning Release build, full unit suite, isolated SQL Server 2022 integration suite, publish artifacts, and deterministic desktop browser smoke with diagnostics retained. SQL-auth container support is opt-in; normal local/production deployment remains integrated authentication. The integration fixture invokes PowerShell Core on Linux. The first hosted GitHub Actions execution requires this committed branch to be pushed; Docker is unavailable in this local workspace.</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="str">
+        <x:v>.github/workflows/release-gate.yml; Deploy-Database; integration fixture; E2E reset/seed/runner; QA framework</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="str">
+        <x:v>19dbc79, 644e6a1</x:v>
+      </x:c>
       <x:c r="K16" s="3" t="str">
-        <x:v>Repository inspection</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="44" customHeight="1">
+        <x:v>Local Release build 0 warnings/0 errors; unit 422/422; SQL integration 124/124; browser smoke 6/6 (16.4s); PowerShell scripts parsed. Hosted Actions container execution pending branch push.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="90" customHeight="1">
       <x:c r="A17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-009</x:t>
@@ -1124,18 +1130,22 @@
         </x:is>
       </x:c>
       <x:c r="G17" s="3" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H17" s="3" t="str">
-        <x:v>Health endpoint exists but distinct liveness/readiness probes are not implemented.</x:v>
-      </x:c>
-      <x:c r="I17" s="3" t="str"/>
-      <x:c r="J17" s="3" t="str"/>
+        <x:v>Added separate API liveness and bounded SQL readiness probes. Liveness has no dependency access; readiness uses a request-scoped context with a five-second deadline; legacy /api/health remains compatible. Detailed diagnostics remain SecurityDiagnostics-protected, log safe access events, and do not return merchant IDs or raw provider validation text. Operational runbooks document the probe policy.</x:v>
+      </x:c>
+      <x:c r="I17" s="3" t="str">
+        <x:v>HealthController; LivenessController; ReadinessProbe; request logging; monitoring/hosting runbooks; health unit/integration tests</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="str">
+        <x:v>ae632fe</x:v>
+      </x:c>
       <x:c r="K17" s="3" t="str">
-        <x:v>Repository inspection</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="44" customHeight="1">
+        <x:v>Release build 0 warnings/0 errors; focused unit 33/33; focused SQL security integration 18/18; full unit 421/421; SQL integration 124/124; Admin monitoring Playwright 6/6 across 3 projects (19.0s), managed teardown clean.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="90" customHeight="1">
       <x:c r="A18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-010</x:t>
@@ -1167,22 +1177,22 @@
         </x:is>
       </x:c>
       <x:c r="G18" s="3" t="str">
-        <x:v>In Progress</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="H18" s="3" t="str">
-        <x:v>Completed inventory in docs/REQ-010-ADMIN-PAGING-INVENTORY.md. Products, orders, payments, wallets, tickets, verification, notifications, coupons, and audit/error/security operational logs now use SQL-side filtered, counted, stable paged endpoints; legacy endpoints remain compatible. Gift-code product selection uses a dedicated bounded lookup. Remaining: detail-history paging, explicit export semantics, focused paging tests, and full verification.</x:v>
+        <x:v>All top-level and nested Admin operational lists are SQL-paged. Product editor variants/media and gift-code variant lookup are bounded; selected product/order exports are server-validated as all-or-nothing, deterministic minimal projections; current-page scope is labeled; SMS export is server-side; CSV formula protection is centralized. The apparent 10-minute issue was expected aggregate runtime: 93 stateful tests run serially over 3 projects. Stable selectors, a 25-minute global cap, timestamped diagnostics, and verified teardown complete the gate.</x:v>
       </x:c>
       <x:c r="I18" s="3" t="str">
-        <x:v>Admin paging inventory; Admin Products/Orders/Payments/Wallets/Tickets/Verifications/Notifications/Coupons/AuditLogs/ErrorLogs/SecurityLogs; paged controllers/read services; GiftCodes lookup</x:v>
+        <x:v>docs/REQ-010-ADMIN-PAGING-INVENTORY.md; AdminProductVariantService; GiftCodes.razor; Admin product/order export controllers; AdminCsv; Playwright config/teardown/runner; paging/export integration and E2E tests</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>8b5fdf7, a885f5c, 02d3354, cd98354, eaee518</x:v>
+        <x:v>8b5fdf7, a885f5c, 02d3354, cd98354, eaee518, a3bdcd5, 22b42a2, d20a3f8, 9016c4a, 2ed2581, 57b9923, 261f705, 2274bea, 4a61f11, 6862950, 6c48ad7</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
-        <x:v>Release builds passed (0 warnings after incremental); focused SQL AdminCatalog suite 3/3; new SQL test host currently hangs before execution and was not retained</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="44" customHeight="1">
+        <x:v>Release build 0 warnings/0 errors; unit 417/417; SQL integration 123/123; focused paging/export SQL 3/3; full Admin Playwright 93/93 passed in 11m29s (exit 0, reporter + teardown complete, no managed API/Web/Node processes); NuGet direct/transitive and npm audits clean. Final scan: remaining Take limits are SQL page caps/lookups or background batch/retention controls. Git: only workbook modified, branch 20 ahead/0 behind.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="90" customHeight="1">
       <x:c r="A19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-011</x:t>
@@ -1225,7 +1235,7 @@
         <x:v>Repository inspection</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="44" customHeight="1">
+    <x:row r="20" ht="90" customHeight="1">
       <x:c r="A20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-012</x:t>
@@ -1268,7 +1278,7 @@
         <x:v>Repository inspection</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="44" customHeight="1">
+    <x:row r="21" ht="90" customHeight="1">
       <x:c r="A21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-013</x:t>
@@ -1311,7 +1321,7 @@
         <x:v>Repository inspection</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="44" customHeight="1">
+    <x:row r="22" ht="90" customHeight="1">
       <x:c r="A22" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-014</x:t>
@@ -1354,7 +1364,7 @@
         <x:v>Repository inspection</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="44" customHeight="1">
+    <x:row r="23" ht="90" customHeight="1">
       <x:c r="A23" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ-015</x:t>
